--- a/Translation Tables/csl_localization_fr_fr.xlsx
+++ b/Translation Tables/csl_localization_fr_fr.xlsx
@@ -848,7 +848,7 @@
     </row>
     <row r="58" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A58" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Briefing</v>
+        <v xml:space="preserve">CSL-UI_RespawnTitle</v>
       </c>
       <c r="B58" t="str">
         <v xml:space="preserve"/>
@@ -856,7 +856,7 @@
     </row>
     <row r="59" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A59" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Debriefing</v>
+        <v xml:space="preserve">CSL-UI_Stage_Briefing</v>
       </c>
       <c r="B59" t="str">
         <v xml:space="preserve"/>
@@ -864,7 +864,7 @@
     </row>
     <row r="60" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A60" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Game</v>
+        <v xml:space="preserve">CSL-UI_Stage_Debriefing</v>
       </c>
       <c r="B60" t="str">
         <v xml:space="preserve"/>
@@ -872,7 +872,7 @@
     </row>
     <row r="61" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A61" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Slotting</v>
+        <v xml:space="preserve">CSL-UI_Stage_Game</v>
       </c>
       <c r="B61" t="str">
         <v xml:space="preserve"/>
@@ -880,7 +880,7 @@
     </row>
     <row r="62" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A62" t="str">
-        <v xml:space="preserve">CSL-UI_Time</v>
+        <v xml:space="preserve">CSL-UI_Stage_Slotting</v>
       </c>
       <c r="B62" t="str">
         <v xml:space="preserve"/>
@@ -888,9 +888,17 @@
     </row>
     <row r="63" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A63" t="str">
+        <v xml:space="preserve">CSL-UI_Time</v>
+      </c>
+      <c r="B63" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="64" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A64" t="str">
         <v xml:space="preserve">CSL-UI_Weather</v>
       </c>
-      <c r="B63" t="str">
+      <c r="B64" t="str">
         <v xml:space="preserve"/>
       </c>
     </row>

--- a/Translation Tables/csl_localization_fr_fr.xlsx
+++ b/Translation Tables/csl_localization_fr_fr.xlsx
@@ -448,7 +448,7 @@
     </row>
     <row r="8" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A8" t="str">
-        <v xml:space="preserve">CSL-Position_DESIGNATED_MARKSMEN</v>
+        <v xml:space="preserve">CSL-Position_COPILOT</v>
       </c>
       <c r="B8" t="str">
         <v xml:space="preserve"/>
@@ -456,7 +456,7 @@
     </row>
     <row r="9" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A9" t="str">
-        <v xml:space="preserve">CSL-Position_EXECUTIVE_OFFICER</v>
+        <v xml:space="preserve">CSL-Position_CREW_CHIEF</v>
       </c>
       <c r="B9" t="str">
         <v xml:space="preserve"/>
@@ -464,7 +464,7 @@
     </row>
     <row r="10" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A10" t="str">
-        <v xml:space="preserve">CSL-Position_FIRST_SERGEANT</v>
+        <v xml:space="preserve">CSL-Position_DESIGNATED_MARKSMEN</v>
       </c>
       <c r="B10" t="str">
         <v xml:space="preserve"/>
@@ -472,7 +472,7 @@
     </row>
     <row r="11" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A11" t="str">
-        <v xml:space="preserve">CSL-Position_GRENADIER</v>
+        <v xml:space="preserve">CSL-Position_EXECUTIVE_OFFICER</v>
       </c>
       <c r="B11" t="str">
         <v xml:space="preserve"/>
@@ -480,7 +480,7 @@
     </row>
     <row r="12" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A12" t="str">
-        <v xml:space="preserve">CSL-Position_MACHINE_GUNNER</v>
+        <v xml:space="preserve">CSL-Position_FIRST_SERGEANT</v>
       </c>
       <c r="B12" t="str">
         <v xml:space="preserve"/>
@@ -488,7 +488,7 @@
     </row>
     <row r="13" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A13" t="str">
-        <v xml:space="preserve">CSL-Position_MEDIC</v>
+        <v xml:space="preserve">CSL-Position_GRENADIER</v>
       </c>
       <c r="B13" t="str">
         <v xml:space="preserve"/>
@@ -496,7 +496,7 @@
     </row>
     <row r="14" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A14" t="str">
-        <v xml:space="preserve">CSL-Position_OPERATIONS_MASTER_SERGEANT</v>
+        <v xml:space="preserve">CSL-Position_MACHINE_GUNNER</v>
       </c>
       <c r="B14" t="str">
         <v xml:space="preserve"/>
@@ -504,7 +504,7 @@
     </row>
     <row r="15" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A15" t="str">
-        <v xml:space="preserve">CSL-Position_OPERATIONS_SERGEANT</v>
+        <v xml:space="preserve">CSL-Position_MEDIC</v>
       </c>
       <c r="B15" t="str">
         <v xml:space="preserve"/>
@@ -512,7 +512,7 @@
     </row>
     <row r="16" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A16" t="str">
-        <v xml:space="preserve">CSL-Position_PLATOON_LEADER</v>
+        <v xml:space="preserve">CSL-Position_OPERATIONS_MASTER_SERGEANT</v>
       </c>
       <c r="B16" t="str">
         <v xml:space="preserve"/>
@@ -520,7 +520,7 @@
     </row>
     <row r="17" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A17" t="str">
-        <v xml:space="preserve">CSL-Position_PLATOON_MEDIC</v>
+        <v xml:space="preserve">CSL-Position_OPERATIONS_SERGEANT</v>
       </c>
       <c r="B17" t="str">
         <v xml:space="preserve"/>
@@ -528,7 +528,7 @@
     </row>
     <row r="18" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A18" t="str">
-        <v xml:space="preserve">CSL-Position_PLATOON_SERGEANT</v>
+        <v xml:space="preserve">CSL-Position_PILOT</v>
       </c>
       <c r="B18" t="str">
         <v xml:space="preserve"/>
@@ -536,7 +536,7 @@
     </row>
     <row r="19" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A19" t="str">
-        <v xml:space="preserve">CSL-Position_RADIO_TELEPHONE_OPERATOR</v>
+        <v xml:space="preserve">CSL-Position_PLATOON_LEADER</v>
       </c>
       <c r="B19" t="str">
         <v xml:space="preserve"/>
@@ -544,7 +544,7 @@
     </row>
     <row r="20" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A20" t="str">
-        <v xml:space="preserve">CSL-Position_RIFLEMAN</v>
+        <v xml:space="preserve">CSL-Position_PLATOON_MEDIC</v>
       </c>
       <c r="B20" t="str">
         <v xml:space="preserve"/>
@@ -552,7 +552,7 @@
     </row>
     <row r="21" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A21" t="str">
-        <v xml:space="preserve">CSL-Position_SENIOR_RADIO_TELEPHONE_OPERATOR</v>
+        <v xml:space="preserve">CSL-Position_PLATOON_SERGEANT</v>
       </c>
       <c r="B21" t="str">
         <v xml:space="preserve"/>
@@ -560,7 +560,7 @@
     </row>
     <row r="22" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A22" t="str">
-        <v xml:space="preserve">CSL-Position_SQUAD_LEADER</v>
+        <v xml:space="preserve">CSL-Position_RADIO_TELEPHONE_OPERATOR</v>
       </c>
       <c r="B22" t="str">
         <v xml:space="preserve"/>
@@ -568,7 +568,7 @@
     </row>
     <row r="23" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A23" t="str">
-        <v xml:space="preserve">CSL-Position_TEAM_LEADER</v>
+        <v xml:space="preserve">CSL-Position_RIFLEMAN</v>
       </c>
       <c r="B23" t="str">
         <v xml:space="preserve"/>
@@ -576,7 +576,7 @@
     </row>
     <row r="24" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A24" t="str">
-        <v xml:space="preserve">CSL-UI-AdminMenu</v>
+        <v xml:space="preserve">CSL-Position_SENIOR_RADIO_TELEPHONE_OPERATOR</v>
       </c>
       <c r="B24" t="str">
         <v xml:space="preserve"/>
@@ -584,7 +584,7 @@
     </row>
     <row r="25" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A25" t="str">
-        <v xml:space="preserve">CSL-UI-AdminMenu_Title</v>
+        <v xml:space="preserve">CSL-Position_SQUAD_LEADER</v>
       </c>
       <c r="B25" t="str">
         <v xml:space="preserve"/>
@@ -592,7 +592,7 @@
     </row>
     <row r="26" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A26" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_AssignSelf</v>
+        <v xml:space="preserve">CSL-Position_TEAM_LEADER</v>
       </c>
       <c r="B26" t="str">
         <v xml:space="preserve"/>
@@ -600,7 +600,7 @@
     </row>
     <row r="27" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A27" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_CloseTicket</v>
+        <v xml:space="preserve">CSL-Position_VEHICLE_COMMANDER</v>
       </c>
       <c r="B27" t="str">
         <v xml:space="preserve"/>
@@ -608,7 +608,7 @@
     </row>
     <row r="28" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A28" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_ForceWakeUp</v>
+        <v xml:space="preserve">CSL-Position_VEHICLE_DRIVER</v>
       </c>
       <c r="B28" t="str">
         <v xml:space="preserve"/>
@@ -616,7 +616,7 @@
     </row>
     <row r="29" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A29" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_Heal</v>
+        <v xml:space="preserve">CSL-Position_VEHICLE_GUNNER</v>
       </c>
       <c r="B29" t="str">
         <v xml:space="preserve"/>
@@ -624,7 +624,7 @@
     </row>
     <row r="30" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A30" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_OpenTickets</v>
+        <v xml:space="preserve">CSL-UI-AdminMenu</v>
       </c>
       <c r="B30" t="str">
         <v xml:space="preserve"/>
@@ -632,7 +632,7 @@
     </row>
     <row r="31" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A31" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_Reply</v>
+        <v xml:space="preserve">CSL-UI-AdminMenu_Title</v>
       </c>
       <c r="B31" t="str">
         <v xml:space="preserve"/>
@@ -640,7 +640,7 @@
     </row>
     <row r="32" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A32" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_SearchPlayer</v>
+        <v xml:space="preserve">CSL-UI-Admin_AssignSelf</v>
       </c>
       <c r="B32" t="str">
         <v xml:space="preserve"/>
@@ -648,7 +648,7 @@
     </row>
     <row r="33" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A33" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_SendAll</v>
+        <v xml:space="preserve">CSL-UI-Admin_CloseTicket</v>
       </c>
       <c r="B33" t="str">
         <v xml:space="preserve"/>
@@ -656,7 +656,7 @@
     </row>
     <row r="34" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A34" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_SendFaction</v>
+        <v xml:space="preserve">CSL-UI-Admin_ForceWakeUp</v>
       </c>
       <c r="B34" t="str">
         <v xml:space="preserve"/>
@@ -664,7 +664,7 @@
     </row>
     <row r="35" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A35" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_SendPlayer</v>
+        <v xml:space="preserve">CSL-UI-Admin_Heal</v>
       </c>
       <c r="B35" t="str">
         <v xml:space="preserve"/>
@@ -672,7 +672,7 @@
     </row>
     <row r="36" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A36" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_SubMenuTitle_Heal</v>
+        <v xml:space="preserve">CSL-UI-Admin_OpenTickets</v>
       </c>
       <c r="B36" t="str">
         <v xml:space="preserve"/>
@@ -680,7 +680,7 @@
     </row>
     <row r="37" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A37" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_SubMenuTitle_Hint</v>
+        <v xml:space="preserve">CSL-UI-Admin_Reply</v>
       </c>
       <c r="B37" t="str">
         <v xml:space="preserve"/>
@@ -688,7 +688,7 @@
     </row>
     <row r="38" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A38" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_SubMenuTitle_Teleport</v>
+        <v xml:space="preserve">CSL-UI-Admin_SearchPlayer</v>
       </c>
       <c r="B38" t="str">
         <v xml:space="preserve"/>
@@ -696,7 +696,7 @@
     </row>
     <row r="39" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A39" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_SubMenuTitle_Tickets</v>
+        <v xml:space="preserve">CSL-UI-Admin_SendAll</v>
       </c>
       <c r="B39" t="str">
         <v xml:space="preserve"/>
@@ -704,7 +704,7 @@
     </row>
     <row r="40" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A40" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_Teleport1</v>
+        <v xml:space="preserve">CSL-UI-Admin_SendFaction</v>
       </c>
       <c r="B40" t="str">
         <v xml:space="preserve"/>
@@ -712,7 +712,7 @@
     </row>
     <row r="41" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A41" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_Teleport2</v>
+        <v xml:space="preserve">CSL-UI-Admin_SendPlayer</v>
       </c>
       <c r="B41" t="str">
         <v xml:space="preserve"/>
@@ -720,7 +720,7 @@
     </row>
     <row r="42" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A42" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_Teleport3</v>
+        <v xml:space="preserve">CSL-UI-Admin_SubMenuTitle_Heal</v>
       </c>
       <c r="B42" t="str">
         <v xml:space="preserve"/>
@@ -728,7 +728,7 @@
     </row>
     <row r="43" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A43" t="str">
-        <v xml:space="preserve">CSL-UI-Admin_Ticket</v>
+        <v xml:space="preserve">CSL-UI-Admin_SubMenuTitle_Hint</v>
       </c>
       <c r="B43" t="str">
         <v xml:space="preserve"/>
@@ -736,7 +736,7 @@
     </row>
     <row r="44" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A44" t="str">
-        <v xml:space="preserve">CSL-UI-CharacterInitialization</v>
+        <v xml:space="preserve">CSL-UI-Admin_SubMenuTitle_Teleport</v>
       </c>
       <c r="B44" t="str">
         <v xml:space="preserve"/>
@@ -744,7 +744,7 @@
     </row>
     <row r="45" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A45" t="str">
-        <v xml:space="preserve">CSL-UI-Factions</v>
+        <v xml:space="preserve">CSL-UI-Admin_SubMenuTitle_Tickets</v>
       </c>
       <c r="B45" t="str">
         <v xml:space="preserve"/>
@@ -752,7 +752,7 @@
     </row>
     <row r="46" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A46" t="str">
-        <v xml:space="preserve">CSL-UI-InOutro_Subtitle1</v>
+        <v xml:space="preserve">CSL-UI-Admin_Teleport1</v>
       </c>
       <c r="B46" t="str">
         <v xml:space="preserve"/>
@@ -760,7 +760,7 @@
     </row>
     <row r="47" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A47" t="str">
-        <v xml:space="preserve">CSL-UI-InOutro_Subtitle2</v>
+        <v xml:space="preserve">CSL-UI-Admin_Teleport2</v>
       </c>
       <c r="B47" t="str">
         <v xml:space="preserve"/>
@@ -768,7 +768,7 @@
     </row>
     <row r="48" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A48" t="str">
-        <v xml:space="preserve">CSL-UI-MissionBy</v>
+        <v xml:space="preserve">CSL-UI-Admin_Teleport3</v>
       </c>
       <c r="B48" t="str">
         <v xml:space="preserve"/>
@@ -776,7 +776,7 @@
     </row>
     <row r="49" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A49" t="str">
-        <v xml:space="preserve">CSL-UI_Back</v>
+        <v xml:space="preserve">CSL-UI-Admin_Ticket</v>
       </c>
       <c r="B49" t="str">
         <v xml:space="preserve"/>
@@ -784,7 +784,7 @@
     </row>
     <row r="50" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A50" t="str">
-        <v xml:space="preserve">CSL-UI_Cancel</v>
+        <v xml:space="preserve">CSL-UI-CharacterInitialization</v>
       </c>
       <c r="B50" t="str">
         <v xml:space="preserve"/>
@@ -792,7 +792,7 @@
     </row>
     <row r="51" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A51" t="str">
-        <v xml:space="preserve">CSL-UI_Confirmation_Text</v>
+        <v xml:space="preserve">CSL-UI-Factions</v>
       </c>
       <c r="B51" t="str">
         <v xml:space="preserve"/>
@@ -800,7 +800,7 @@
     </row>
     <row r="52" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A52" t="str">
-        <v xml:space="preserve">CSL-UI_Empty</v>
+        <v xml:space="preserve">CSL-UI-InOutro_Subtitle1</v>
       </c>
       <c r="B52" t="str">
         <v xml:space="preserve"/>
@@ -808,7 +808,7 @@
     </row>
     <row r="53" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A53" t="str">
-        <v xml:space="preserve">CSL-UI_Execute</v>
+        <v xml:space="preserve">CSL-UI-InOutro_Subtitle2</v>
       </c>
       <c r="B53" t="str">
         <v xml:space="preserve"/>
@@ -816,7 +816,7 @@
     </row>
     <row r="54" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A54" t="str">
-        <v xml:space="preserve">CSL-UI_List</v>
+        <v xml:space="preserve">CSL-UI-MissionBy</v>
       </c>
       <c r="B54" t="str">
         <v xml:space="preserve"/>
@@ -824,7 +824,7 @@
     </row>
     <row r="55" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A55" t="str">
-        <v xml:space="preserve">CSL-UI_ListUnslotted</v>
+        <v xml:space="preserve">CSL-UI_Back</v>
       </c>
       <c r="B55" t="str">
         <v xml:space="preserve"/>
@@ -832,7 +832,7 @@
     </row>
     <row r="56" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A56" t="str">
-        <v xml:space="preserve">CSL-UI_Player</v>
+        <v xml:space="preserve">CSL-UI_Cancel</v>
       </c>
       <c r="B56" t="str">
         <v xml:space="preserve"/>
@@ -840,7 +840,7 @@
     </row>
     <row r="57" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A57" t="str">
-        <v xml:space="preserve">CSL-UI_Players</v>
+        <v xml:space="preserve">CSL-UI_Confirmation_Text</v>
       </c>
       <c r="B57" t="str">
         <v xml:space="preserve"/>
@@ -848,7 +848,7 @@
     </row>
     <row r="58" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A58" t="str">
-        <v xml:space="preserve">CSL-UI_RespawnTitle</v>
+        <v xml:space="preserve">CSL-UI_Empty</v>
       </c>
       <c r="B58" t="str">
         <v xml:space="preserve"/>
@@ -856,7 +856,7 @@
     </row>
     <row r="59" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A59" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Briefing</v>
+        <v xml:space="preserve">CSL-UI_Execute</v>
       </c>
       <c r="B59" t="str">
         <v xml:space="preserve"/>
@@ -864,7 +864,7 @@
     </row>
     <row r="60" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A60" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Debriefing</v>
+        <v xml:space="preserve">CSL-UI_List</v>
       </c>
       <c r="B60" t="str">
         <v xml:space="preserve"/>
@@ -872,7 +872,7 @@
     </row>
     <row r="61" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A61" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Game</v>
+        <v xml:space="preserve">CSL-UI_ListUnslotted</v>
       </c>
       <c r="B61" t="str">
         <v xml:space="preserve"/>
@@ -880,7 +880,7 @@
     </row>
     <row r="62" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A62" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Slotting</v>
+        <v xml:space="preserve">CSL-UI_Player</v>
       </c>
       <c r="B62" t="str">
         <v xml:space="preserve"/>
@@ -888,7 +888,7 @@
     </row>
     <row r="63" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A63" t="str">
-        <v xml:space="preserve">CSL-UI_Time</v>
+        <v xml:space="preserve">CSL-UI_Players</v>
       </c>
       <c r="B63" t="str">
         <v xml:space="preserve"/>
@@ -896,9 +896,57 @@
     </row>
     <row r="64" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A64" t="str">
+        <v xml:space="preserve">CSL-UI_RespawnTitle</v>
+      </c>
+      <c r="B64" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="65" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A65" t="str">
+        <v xml:space="preserve">CSL-UI_Stage_Briefing</v>
+      </c>
+      <c r="B65" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="66" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A66" t="str">
+        <v xml:space="preserve">CSL-UI_Stage_Debriefing</v>
+      </c>
+      <c r="B66" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="67" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A67" t="str">
+        <v xml:space="preserve">CSL-UI_Stage_Game</v>
+      </c>
+      <c r="B67" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="68" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A68" t="str">
+        <v xml:space="preserve">CSL-UI_Stage_Slotting</v>
+      </c>
+      <c r="B68" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="69" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A69" t="str">
+        <v xml:space="preserve">CSL-UI_Time</v>
+      </c>
+      <c r="B69" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="70" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A70" t="str">
         <v xml:space="preserve">CSL-UI_Weather</v>
       </c>
-      <c r="B64" t="str">
+      <c r="B70" t="str">
         <v xml:space="preserve"/>
       </c>
     </row>
